--- a/outputs/space-attack-prompts/prompts.xlsx
+++ b/outputs/space-attack-prompts/prompts.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R3df96b8ffc4049e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R4dc36f2f3d494a09"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -327,6 +327,17 @@
 - Collision detection should also be added to the ship.</x:v>
       </x:c>
     </x:row>
+    <x:row r="5" ht="120" customHeight="1">
+      <x:c r="A5" s="9" t="n">
+        <x:v>46301.44130787037</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>All right, excellent. The ship and projectile seem to be working on my review. Let's move on to adding three game states and find the data variables for those states to this game:
+- Start, which will include instructions for the controls for the game and will wipe any previous playing game state data to a clean slate on initialization.
+- Playing, which will track the number of ship lives, overall score, and wave number that the player is currently facing.
+- Game Over, which will freeze the gameplay state and offer the player the option to start again.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/space-attack-prompts/prompts.xlsx
+++ b/outputs/space-attack-prompts/prompts.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R4dc36f2f3d494a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="Raa1e2c56e70c4e70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,8 +13,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd hh:mm:ss"/>
+    <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd hh:mm:ss &quot;PDT&quot;"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -52,7 +53,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -79,6 +80,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -338,6 +340,53 @@
 - Game Over, which will freeze the gameplay state and offer the player the option to start again.</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" ht="220" customHeight="1">
+      <x:c r="A6" s="9" t="n">
+        <x:v>46301.452685185184</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>All right, excellent. The ship and projectile seem to be working on my review. Let's move on to adding three game states and find the data variables for those states to this game:
+- Start, which will include instructions for the controls for the game and will wipe any previous playing game state data to a clean slate on initialization.
+- Playing, which will track the number of ship lives, overall score, and wave number that the player is currently facing.
+- Game Over, which will freeze the gameplay state and offer the player the option to start again.
+Build me a debug key that will be removed before publishing so that I can hit P to instantly remove all remaining lives, and which should take me to the game over state for testing.
+Let's start working on defining the enemy. The enemy's size and hitbox should be a 32x32 point square. The image should be of an 8-bit style spaceship in a single color, initially defined as red. The enemy emits a projectile 2 points wide by 16 points tall, the same color as that enemy, in a 3-second cycle. Every 3 seconds, the enemy has a chance to fire a projectile.
+The enemy has two states:
+- Formation state: the chance to emit a projectile in each 3-second cycle is 0.3.
+- Advancing state: the chance to emit a projectile is 0.8, with 1 being a 100% chance to emit a projectile.
+If that projectile hits the ship, the lives counter decrements by 1.
+Place an initial enemy object at the center top of the canvas, 24 points below the top HUD objects, so it should appear 20 points below the score counter.
+Also change the name of this game to "Space Attack" on the start screen and on the web page name itself.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="100" customHeight="1">
+      <x:c r="A7" s="9" t="n">
+        <x:v>46301.46314814815</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>Okay, that seems to be working. Now let's add logic so that:
+- Each time a ship-emitted projectile hits an enemy, both the projectile that hit the enemy and the enemy are removed from the game, and the score is increased by 100 points.
+- When an enemy projectile hits the ship, causing a depreciation of lives, the ship should flash black three times before returning to its bright green state.
+- For testing purposes, place an initial grid of enemies that is 4x4 at the top of the screen. They should all be in just the formation state.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="140" customHeight="1">
+      <x:c r="A8" s="9" t="n">
+        <x:v>46301.47012731482</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>Increase the velocity of all projectiles to 2. Decrease the chance for an enemy in formation state to emit a projectile by half of current rate.
+Now let's define the Formation state movement. In Formation state, the enemy grid will move right at speed 0.4 until the grid reaches a point within 64 pt of the canvas edge, and then changes direction to begin moving left. The grid shifts direction again when it reaches 64 pt or less of the left edge. Each time the grid reaches an edge, the grid descends 64 pts and its speed increases x1.2.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="n">
+        <x:v>46301.479722222226</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Now let's add Wave tracking and initialization. When the last enemy on the screen has been removed, increment the wave counter by 1 and add a fresh grid of enemies to the board. The first wave of enemies should be a grid of 4 columns by 2 rows. With each additional wave, multiply the number of enemies by 1.2. Distribute enemies symmetrically across the center with a maximum grid width of 16 enemies and maximum of 6 rows. If a wave would exceed the maximum number of enemies, the Formation start speed is instead increased by x1.5. Also, if an enemy reaches the bottom of the canvas, deprecate the Lives by 1.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/space-attack-prompts/prompts.xlsx
+++ b/outputs/space-attack-prompts/prompts.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="Raa1e2c56e70c4e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R0379f80184314020"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -387,6 +387,15 @@
         <x:v>Now let's add Wave tracking and initialization. When the last enemy on the screen has been removed, increment the wave counter by 1 and add a fresh grid of enemies to the board. The first wave of enemies should be a grid of 4 columns by 2 rows. With each additional wave, multiply the number of enemies by 1.2. Distribute enemies symmetrically across the center with a maximum grid width of 16 enemies and maximum of 6 rows. If a wave would exceed the maximum number of enemies, the Formation start speed is instead increased by x1.5. Also, if an enemy reaches the bottom of the canvas, deprecate the Lives by 1.</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="n">
+        <x:v>46301.48673611111</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>there is currently a bug where, when an enemy is removed from a row, the other enemies in the row shift toward the center. When an enemy is removed via projectile hit, all remaining enemies in the grid should retain their placement. Same goes for upcoming advancing enemy state: if an enemy leaves the grid for any reason, the rest of the enemy formation grid should retain its position relative to the grid.
+Also, with each wave, let's increase the speed of the formation grid by 1.2, so that every wave is faster than the last one. Once the enemy grid is maximum size, then instead increase subsequent waves' starting speed by 1.5. Also, let's increase the formation grid direction speed change to 1.3 instead of 1.2.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/space-attack-prompts/prompts.xlsx
+++ b/outputs/space-attack-prompts/prompts.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R0379f80184314020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R7237a0bb4ed34cc8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -396,6 +396,16 @@
 Also, with each wave, let's increase the speed of the formation grid by 1.2, so that every wave is faster than the last one. Once the enemy grid is maximum size, then instead increase subsequent waves' starting speed by 1.5. Also, let's increase the formation grid direction speed change to 1.3 instead of 1.2.</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="n">
+        <x:v>46301.494525462964</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Double the delay for ship projectile firing. Change the increase in number of enemies per wave to a multiplier of 1.3.
+Let's now add an advancing state to the enemies. With each firing chance roll that currently occurs every 3 seconds, there is also a 0.1 chance that an enemy will shift into the advancing state.
+In the advancing state, the enemy will leave the group of enemies and begin a descending velocity of 1.4. It will fire a projectile every second while advancing. While advancing, the enemy's horizontal movement is bounded on the left and right sides by 248 points, unless the enemy hits the side of the canvas, at which point it will always change directions. The enemy should, when it goes into an advancing mode, leave the grid, descend toward the bottom of the screen while firing and drifting from left to right.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/space-attack-prompts/prompts.xlsx
+++ b/outputs/space-attack-prompts/prompts.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R7237a0bb4ed34cc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R9c2bd2c87ca941f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -406,6 +406,14 @@
 In the advancing state, the enemy will leave the group of enemies and begin a descending velocity of 1.4. It will fire a projectile every second while advancing. While advancing, the enemy's horizontal movement is bounded on the left and right sides by 248 points, unless the enemy hits the side of the canvas, at which point it will always change directions. The enemy should, when it goes into an advancing mode, leave the grid, descend toward the bottom of the screen while firing and drifting from left to right.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="n">
+        <x:v>46301.50431712963</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Change white text font size to 20 on the start state and the gameplay HUD.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/space-attack-prompts/prompts.xlsx
+++ b/outputs/space-attack-prompts/prompts.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R9c2bd2c87ca941f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="1" r:id="R4723a5c28c1d4055"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -414,6 +414,14 @@
         <x:v>Change white text font size to 20 on the start state and the gameplay HUD.</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="n">
+        <x:v>46301.50592592593</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>publish this site using Codex Sites</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
